--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -112,8 +118,13 @@
         <fgColor rgb="008B1E22"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -179,11 +190,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -378,6 +403,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -612,13 +643,13 @@
 (직접 입력)</t>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <t>▣ 상태
 (직접 입력)</t>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <t>▣ 메모
 (직접 입력)</t>
@@ -918,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -937,7 +968,7 @@
     <col width="12" customWidth="1" style="55" min="14" max="14"/>
     <col width="12" customWidth="1" style="55" min="15" max="15"/>
     <col width="6" customWidth="1" style="55" min="16" max="16"/>
-    <col width="10" customWidth="1" style="55" min="17" max="17"/>
+    <col width="12" customWidth="1" style="55" min="17" max="17"/>
     <col width="28" customWidth="1" style="55" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -962,8 +993,8 @@
       <c r="N1" s="16" t="n"/>
       <c r="O1" s="16" t="n"/>
       <c r="P1" s="16" t="n"/>
-      <c r="Q1" s="16" t="n"/>
-      <c r="R1" s="17" t="n"/>
+      <c r="R1" s="16" t="n"/>
+      <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="63" t="inlineStr">
@@ -986,8 +1017,8 @@
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="16" t="n"/>
-      <c r="Q2" s="17" t="n"/>
-      <c r="R2" s="64" t="inlineStr">
+      <c r="R2" s="17" t="n"/>
+      <c r="S2" s="64" t="inlineStr">
         <is>
           <t>업데이트: 2026-05-02 01:42</t>
         </is>
@@ -1074,12 +1105,17 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="Q3" s="65" t="inlineStr">
+        <is>
+          <t>✏입력</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1166,12 +1202,18 @@
           <t>입고</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="Q4" s="66" t="inlineStr">
+        <is>
+          <t>외주
+입고일</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1230,8 +1272,8 @@
       <c r="N5" s="11" t="n"/>
       <c r="O5" s="11" t="n"/>
       <c r="P5" s="11" t="n"/>
-      <c r="Q5" s="9" t="n"/>
-      <c r="R5" s="22" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1286,8 +1328,8 @@
       <c r="N6" s="15" t="n"/>
       <c r="O6" s="15" t="n"/>
       <c r="P6" s="15" t="n"/>
-      <c r="Q6" s="13" t="n"/>
-      <c r="R6" s="24" t="n"/>
+      <c r="R6" s="13" t="n"/>
+      <c r="S6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1340,8 +1382,8 @@
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
-      <c r="Q7" s="9" t="n"/>
-      <c r="R7" s="22" t="n"/>
+      <c r="R7" s="9" t="n"/>
+      <c r="S7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1394,8 +1436,8 @@
       <c r="N8" s="15" t="n"/>
       <c r="O8" s="15" t="n"/>
       <c r="P8" s="15" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="24" t="n"/>
+      <c r="R8" s="13" t="n"/>
+      <c r="S8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1448,8 +1490,8 @@
       <c r="N9" s="11" t="n"/>
       <c r="O9" s="11" t="n"/>
       <c r="P9" s="11" t="n"/>
-      <c r="Q9" s="9" t="n"/>
-      <c r="R9" s="22" t="n"/>
+      <c r="R9" s="9" t="n"/>
+      <c r="S9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1502,8 +1544,8 @@
       <c r="N10" s="15" t="n"/>
       <c r="O10" s="15" t="n"/>
       <c r="P10" s="15" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="24" t="n"/>
+      <c r="R10" s="13" t="n"/>
+      <c r="S10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1556,8 +1598,8 @@
       <c r="N11" s="11" t="n"/>
       <c r="O11" s="11" t="n"/>
       <c r="P11" s="11" t="n"/>
-      <c r="Q11" s="9" t="n"/>
-      <c r="R11" s="22" t="n"/>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -1610,8 +1652,8 @@
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="15" t="n"/>
       <c r="P12" s="15" t="n"/>
-      <c r="Q12" s="13" t="n"/>
-      <c r="R12" s="24" t="n"/>
+      <c r="R12" s="13" t="n"/>
+      <c r="S12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1664,8 +1706,8 @@
       <c r="N13" s="11" t="n"/>
       <c r="O13" s="11" t="n"/>
       <c r="P13" s="11" t="n"/>
-      <c r="Q13" s="9" t="n"/>
-      <c r="R13" s="22" t="n"/>
+      <c r="R13" s="9" t="n"/>
+      <c r="S13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -1718,8 +1760,8 @@
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="15" t="n"/>
       <c r="P14" s="15" t="n"/>
-      <c r="Q14" s="13" t="n"/>
-      <c r="R14" s="24" t="n"/>
+      <c r="R14" s="13" t="n"/>
+      <c r="S14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -1772,8 +1814,8 @@
       <c r="N15" s="11" t="n"/>
       <c r="O15" s="11" t="n"/>
       <c r="P15" s="11" t="n"/>
-      <c r="Q15" s="9" t="n"/>
-      <c r="R15" s="22" t="n"/>
+      <c r="R15" s="9" t="n"/>
+      <c r="S15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -1828,8 +1870,8 @@
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
       <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="13" t="n"/>
-      <c r="R16" s="24" t="n"/>
+      <c r="R16" s="13" t="n"/>
+      <c r="S16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -1884,8 +1926,8 @@
       <c r="N17" s="11" t="n"/>
       <c r="O17" s="11" t="n"/>
       <c r="P17" s="11" t="n"/>
-      <c r="Q17" s="9" t="n"/>
-      <c r="R17" s="22" t="n"/>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -1938,8 +1980,8 @@
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
       <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="13" t="n"/>
-      <c r="R18" s="24" t="n"/>
+      <c r="R18" s="13" t="n"/>
+      <c r="S18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -1992,8 +2034,8 @@
       <c r="N19" s="11" t="n"/>
       <c r="O19" s="11" t="n"/>
       <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="22" t="n"/>
+      <c r="R19" s="9" t="n"/>
+      <c r="S19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2046,8 +2088,8 @@
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
       <c r="P20" s="15" t="n"/>
-      <c r="Q20" s="13" t="n"/>
-      <c r="R20" s="24" t="n"/>
+      <c r="R20" s="13" t="n"/>
+      <c r="S20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2100,8 +2142,8 @@
       <c r="N21" s="11" t="n"/>
       <c r="O21" s="11" t="n"/>
       <c r="P21" s="11" t="n"/>
-      <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="22" t="n"/>
+      <c r="R21" s="9" t="n"/>
+      <c r="S21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2154,8 +2196,8 @@
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
       <c r="P22" s="15" t="n"/>
-      <c r="Q22" s="13" t="n"/>
-      <c r="R22" s="24" t="n"/>
+      <c r="R22" s="13" t="n"/>
+      <c r="S22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2208,8 +2250,8 @@
       <c r="N23" s="11" t="n"/>
       <c r="O23" s="11" t="n"/>
       <c r="P23" s="11" t="n"/>
-      <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="22" t="n"/>
+      <c r="R23" s="9" t="n"/>
+      <c r="S23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2262,8 +2304,8 @@
       <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="n"/>
       <c r="P24" s="15" t="n"/>
-      <c r="Q24" s="13" t="n"/>
-      <c r="R24" s="24" t="n"/>
+      <c r="R24" s="13" t="n"/>
+      <c r="S24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2316,8 +2358,8 @@
       <c r="N25" s="11" t="n"/>
       <c r="O25" s="11" t="n"/>
       <c r="P25" s="11" t="n"/>
-      <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="22" t="n"/>
+      <c r="R25" s="9" t="n"/>
+      <c r="S25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2370,8 +2412,8 @@
       <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="n"/>
       <c r="P26" s="15" t="n"/>
-      <c r="Q26" s="13" t="n"/>
-      <c r="R26" s="24" t="n"/>
+      <c r="R26" s="13" t="n"/>
+      <c r="S26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2424,8 +2466,8 @@
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
       <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="22" t="n"/>
+      <c r="R27" s="9" t="n"/>
+      <c r="S27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n"/>
@@ -2444,8 +2486,8 @@
       <c r="N28" s="13" t="n"/>
       <c r="O28" s="13" t="n"/>
       <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="13" t="n"/>
-      <c r="R28" s="24" t="n"/>
+      <c r="R28" s="13" t="n"/>
+      <c r="S28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n"/>
@@ -2464,8 +2506,8 @@
       <c r="N29" s="9" t="n"/>
       <c r="O29" s="9" t="n"/>
       <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="9" t="n"/>
-      <c r="R29" s="22" t="n"/>
+      <c r="R29" s="9" t="n"/>
+      <c r="S29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n"/>
@@ -2484,8 +2526,8 @@
       <c r="N30" s="13" t="n"/>
       <c r="O30" s="13" t="n"/>
       <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="13" t="n"/>
-      <c r="R30" s="24" t="n"/>
+      <c r="R30" s="13" t="n"/>
+      <c r="S30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n"/>
@@ -2504,8 +2546,8 @@
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="9" t="n"/>
       <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="22" t="n"/>
+      <c r="R31" s="9" t="n"/>
+      <c r="S31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n"/>
@@ -2524,8 +2566,8 @@
       <c r="N32" s="13" t="n"/>
       <c r="O32" s="13" t="n"/>
       <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="13" t="n"/>
-      <c r="R32" s="24" t="n"/>
+      <c r="R32" s="13" t="n"/>
+      <c r="S32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n"/>
@@ -2544,8 +2586,8 @@
       <c r="N33" s="9" t="n"/>
       <c r="O33" s="9" t="n"/>
       <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="9" t="n"/>
-      <c r="R33" s="22" t="n"/>
+      <c r="R33" s="9" t="n"/>
+      <c r="S33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n"/>
@@ -2564,8 +2606,8 @@
       <c r="N34" s="13" t="n"/>
       <c r="O34" s="13" t="n"/>
       <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="13" t="n"/>
-      <c r="R34" s="24" t="n"/>
+      <c r="R34" s="13" t="n"/>
+      <c r="S34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n"/>
@@ -2584,8 +2626,8 @@
       <c r="N35" s="9" t="n"/>
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="22" t="n"/>
+      <c r="R35" s="9" t="n"/>
+      <c r="S35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n"/>
@@ -2604,8 +2646,8 @@
       <c r="N36" s="13" t="n"/>
       <c r="O36" s="13" t="n"/>
       <c r="P36" s="13" t="n"/>
-      <c r="Q36" s="13" t="n"/>
-      <c r="R36" s="24" t="n"/>
+      <c r="R36" s="13" t="n"/>
+      <c r="S36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n"/>
@@ -2624,8 +2666,8 @@
       <c r="N37" s="9" t="n"/>
       <c r="O37" s="9" t="n"/>
       <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="22" t="n"/>
+      <c r="R37" s="9" t="n"/>
+      <c r="S37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n"/>
@@ -2644,8 +2686,8 @@
       <c r="N38" s="13" t="n"/>
       <c r="O38" s="13" t="n"/>
       <c r="P38" s="13" t="n"/>
-      <c r="Q38" s="13" t="n"/>
-      <c r="R38" s="24" t="n"/>
+      <c r="R38" s="13" t="n"/>
+      <c r="S38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n"/>
@@ -2664,8 +2706,8 @@
       <c r="N39" s="9" t="n"/>
       <c r="O39" s="9" t="n"/>
       <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="9" t="n"/>
-      <c r="R39" s="22" t="n"/>
+      <c r="R39" s="9" t="n"/>
+      <c r="S39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n"/>
@@ -2684,8 +2726,8 @@
       <c r="N40" s="13" t="n"/>
       <c r="O40" s="13" t="n"/>
       <c r="P40" s="13" t="n"/>
-      <c r="Q40" s="13" t="n"/>
-      <c r="R40" s="24" t="n"/>
+      <c r="R40" s="13" t="n"/>
+      <c r="S40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n"/>
@@ -2704,8 +2746,8 @@
       <c r="N41" s="9" t="n"/>
       <c r="O41" s="9" t="n"/>
       <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
-      <c r="R41" s="22" t="n"/>
+      <c r="R41" s="9" t="n"/>
+      <c r="S41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n"/>
@@ -2724,8 +2766,8 @@
       <c r="N42" s="13" t="n"/>
       <c r="O42" s="13" t="n"/>
       <c r="P42" s="13" t="n"/>
-      <c r="Q42" s="13" t="n"/>
-      <c r="R42" s="24" t="n"/>
+      <c r="R42" s="13" t="n"/>
+      <c r="S42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n"/>
@@ -2744,8 +2786,8 @@
       <c r="N43" s="9" t="n"/>
       <c r="O43" s="9" t="n"/>
       <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="9" t="n"/>
-      <c r="R43" s="22" t="n"/>
+      <c r="R43" s="9" t="n"/>
+      <c r="S43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n"/>
@@ -2764,8 +2806,8 @@
       <c r="N44" s="13" t="n"/>
       <c r="O44" s="13" t="n"/>
       <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="13" t="n"/>
-      <c r="R44" s="24" t="n"/>
+      <c r="R44" s="13" t="n"/>
+      <c r="S44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n"/>
@@ -2784,8 +2826,8 @@
       <c r="N45" s="9" t="n"/>
       <c r="O45" s="9" t="n"/>
       <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="9" t="n"/>
-      <c r="R45" s="22" t="n"/>
+      <c r="R45" s="9" t="n"/>
+      <c r="S45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n"/>
@@ -2804,8 +2846,8 @@
       <c r="N46" s="13" t="n"/>
       <c r="O46" s="13" t="n"/>
       <c r="P46" s="13" t="n"/>
-      <c r="Q46" s="13" t="n"/>
-      <c r="R46" s="24" t="n"/>
+      <c r="R46" s="13" t="n"/>
+      <c r="S46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n"/>
@@ -2824,8 +2866,8 @@
       <c r="N47" s="9" t="n"/>
       <c r="O47" s="9" t="n"/>
       <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="9" t="n"/>
-      <c r="R47" s="22" t="n"/>
+      <c r="R47" s="9" t="n"/>
+      <c r="S47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n"/>
@@ -2844,8 +2886,8 @@
       <c r="N48" s="13" t="n"/>
       <c r="O48" s="13" t="n"/>
       <c r="P48" s="13" t="n"/>
-      <c r="Q48" s="13" t="n"/>
-      <c r="R48" s="24" t="n"/>
+      <c r="R48" s="13" t="n"/>
+      <c r="S48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n"/>
@@ -2864,8 +2906,8 @@
       <c r="N49" s="9" t="n"/>
       <c r="O49" s="9" t="n"/>
       <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="9" t="n"/>
-      <c r="R49" s="22" t="n"/>
+      <c r="R49" s="9" t="n"/>
+      <c r="S49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n"/>
@@ -2884,8 +2926,8 @@
       <c r="N50" s="13" t="n"/>
       <c r="O50" s="13" t="n"/>
       <c r="P50" s="13" t="n"/>
-      <c r="Q50" s="13" t="n"/>
-      <c r="R50" s="24" t="n"/>
+      <c r="R50" s="13" t="n"/>
+      <c r="S50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n"/>
@@ -2904,8 +2946,8 @@
       <c r="N51" s="9" t="n"/>
       <c r="O51" s="9" t="n"/>
       <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="9" t="n"/>
-      <c r="R51" s="22" t="n"/>
+      <c r="R51" s="9" t="n"/>
+      <c r="S51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n"/>
@@ -2924,8 +2966,8 @@
       <c r="N52" s="13" t="n"/>
       <c r="O52" s="13" t="n"/>
       <c r="P52" s="13" t="n"/>
-      <c r="Q52" s="13" t="n"/>
-      <c r="R52" s="24" t="n"/>
+      <c r="R52" s="13" t="n"/>
+      <c r="S52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n"/>
@@ -2944,8 +2986,8 @@
       <c r="N53" s="9" t="n"/>
       <c r="O53" s="9" t="n"/>
       <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="9" t="n"/>
-      <c r="R53" s="22" t="n"/>
+      <c r="R53" s="9" t="n"/>
+      <c r="S53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n"/>
@@ -2964,8 +3006,8 @@
       <c r="N54" s="13" t="n"/>
       <c r="O54" s="13" t="n"/>
       <c r="P54" s="13" t="n"/>
-      <c r="Q54" s="13" t="n"/>
-      <c r="R54" s="24" t="n"/>
+      <c r="R54" s="13" t="n"/>
+      <c r="S54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n"/>
@@ -2984,8 +3026,8 @@
       <c r="N55" s="9" t="n"/>
       <c r="O55" s="9" t="n"/>
       <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="9" t="n"/>
-      <c r="R55" s="22" t="n"/>
+      <c r="R55" s="9" t="n"/>
+      <c r="S55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n"/>
@@ -3004,8 +3046,8 @@
       <c r="N56" s="13" t="n"/>
       <c r="O56" s="13" t="n"/>
       <c r="P56" s="13" t="n"/>
-      <c r="Q56" s="13" t="n"/>
-      <c r="R56" s="24" t="n"/>
+      <c r="R56" s="13" t="n"/>
+      <c r="S56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n"/>
@@ -3024,8 +3066,8 @@
       <c r="N57" s="9" t="n"/>
       <c r="O57" s="9" t="n"/>
       <c r="P57" s="9" t="n"/>
-      <c r="Q57" s="9" t="n"/>
-      <c r="R57" s="22" t="n"/>
+      <c r="R57" s="9" t="n"/>
+      <c r="S57" s="22" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -408,6 +408,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -640,6 +652,13 @@
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <t>▣ 입고
+(직접 입력)</t>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 외주
+입고일
 (직접 입력)</t>
       </text>
     </comment>
@@ -969,11 +988,12 @@
     <col width="12" customWidth="1" style="55" min="15" max="15"/>
     <col width="6" customWidth="1" style="55" min="16" max="16"/>
     <col width="12" customWidth="1" style="55" min="17" max="17"/>
-    <col width="28" customWidth="1" style="55" min="18" max="18"/>
+    <col width="10" customWidth="1" style="55" min="18" max="18"/>
+    <col width="28" customWidth="1" style="55" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -993,11 +1013,12 @@
       <c r="N1" s="16" t="n"/>
       <c r="O1" s="16" t="n"/>
       <c r="P1" s="16" t="n"/>
+      <c r="Q1" s="16" t="n"/>
       <c r="R1" s="16" t="n"/>
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="68" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1017,10 +1038,11 @@
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="64" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:42</t>
+      <c r="S2" s="69" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:45</t>
         </is>
       </c>
     </row>
@@ -1105,9 +1127,9 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="Q3" s="65" t="inlineStr">
-        <is>
-          <t>✏입력</t>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -1202,7 +1224,7 @@
           <t>입고</t>
         </is>
       </c>
-      <c r="Q4" s="66" t="inlineStr">
+      <c r="Q4" s="70" t="inlineStr">
         <is>
           <t>외주
 입고일</t>
@@ -1272,6 +1294,7 @@
       <c r="N5" s="11" t="n"/>
       <c r="O5" s="11" t="n"/>
       <c r="P5" s="11" t="n"/>
+      <c r="Q5" s="9" t="n"/>
       <c r="R5" s="9" t="n"/>
       <c r="S5" s="22" t="n"/>
     </row>
@@ -1328,6 +1351,7 @@
       <c r="N6" s="15" t="n"/>
       <c r="O6" s="15" t="n"/>
       <c r="P6" s="15" t="n"/>
+      <c r="Q6" s="13" t="n"/>
       <c r="R6" s="13" t="n"/>
       <c r="S6" s="24" t="n"/>
     </row>
@@ -1382,6 +1406,7 @@
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
+      <c r="Q7" s="9" t="n"/>
       <c r="R7" s="9" t="n"/>
       <c r="S7" s="22" t="n"/>
     </row>
@@ -1436,6 +1461,7 @@
       <c r="N8" s="15" t="n"/>
       <c r="O8" s="15" t="n"/>
       <c r="P8" s="15" t="n"/>
+      <c r="Q8" s="13" t="n"/>
       <c r="R8" s="13" t="n"/>
       <c r="S8" s="24" t="n"/>
     </row>
@@ -1490,6 +1516,7 @@
       <c r="N9" s="11" t="n"/>
       <c r="O9" s="11" t="n"/>
       <c r="P9" s="11" t="n"/>
+      <c r="Q9" s="9" t="n"/>
       <c r="R9" s="9" t="n"/>
       <c r="S9" s="22" t="n"/>
     </row>
@@ -1544,6 +1571,7 @@
       <c r="N10" s="15" t="n"/>
       <c r="O10" s="15" t="n"/>
       <c r="P10" s="15" t="n"/>
+      <c r="Q10" s="13" t="n"/>
       <c r="R10" s="13" t="n"/>
       <c r="S10" s="24" t="n"/>
     </row>
@@ -1598,6 +1626,7 @@
       <c r="N11" s="11" t="n"/>
       <c r="O11" s="11" t="n"/>
       <c r="P11" s="11" t="n"/>
+      <c r="Q11" s="9" t="n"/>
       <c r="R11" s="9" t="n"/>
       <c r="S11" s="22" t="n"/>
     </row>
@@ -1652,6 +1681,7 @@
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="15" t="n"/>
       <c r="P12" s="15" t="n"/>
+      <c r="Q12" s="13" t="n"/>
       <c r="R12" s="13" t="n"/>
       <c r="S12" s="24" t="n"/>
     </row>
@@ -1706,6 +1736,7 @@
       <c r="N13" s="11" t="n"/>
       <c r="O13" s="11" t="n"/>
       <c r="P13" s="11" t="n"/>
+      <c r="Q13" s="9" t="n"/>
       <c r="R13" s="9" t="n"/>
       <c r="S13" s="22" t="n"/>
     </row>
@@ -1760,6 +1791,7 @@
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="15" t="n"/>
       <c r="P14" s="15" t="n"/>
+      <c r="Q14" s="13" t="n"/>
       <c r="R14" s="13" t="n"/>
       <c r="S14" s="24" t="n"/>
     </row>
@@ -1814,6 +1846,7 @@
       <c r="N15" s="11" t="n"/>
       <c r="O15" s="11" t="n"/>
       <c r="P15" s="11" t="n"/>
+      <c r="Q15" s="9" t="n"/>
       <c r="R15" s="9" t="n"/>
       <c r="S15" s="22" t="n"/>
     </row>
@@ -1870,6 +1903,7 @@
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
       <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="13" t="n"/>
       <c r="R16" s="13" t="n"/>
       <c r="S16" s="24" t="n"/>
     </row>
@@ -1926,6 +1960,7 @@
       <c r="N17" s="11" t="n"/>
       <c r="O17" s="11" t="n"/>
       <c r="P17" s="11" t="n"/>
+      <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
       <c r="S17" s="22" t="n"/>
     </row>
@@ -1980,6 +2015,7 @@
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
       <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="13" t="n"/>
       <c r="R18" s="13" t="n"/>
       <c r="S18" s="24" t="n"/>
     </row>
@@ -2034,6 +2070,7 @@
       <c r="N19" s="11" t="n"/>
       <c r="O19" s="11" t="n"/>
       <c r="P19" s="11" t="n"/>
+      <c r="Q19" s="9" t="n"/>
       <c r="R19" s="9" t="n"/>
       <c r="S19" s="22" t="n"/>
     </row>
@@ -2088,6 +2125,7 @@
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
       <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="13" t="n"/>
       <c r="R20" s="13" t="n"/>
       <c r="S20" s="24" t="n"/>
     </row>
@@ -2142,6 +2180,7 @@
       <c r="N21" s="11" t="n"/>
       <c r="O21" s="11" t="n"/>
       <c r="P21" s="11" t="n"/>
+      <c r="Q21" s="9" t="n"/>
       <c r="R21" s="9" t="n"/>
       <c r="S21" s="22" t="n"/>
     </row>
@@ -2196,6 +2235,7 @@
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
       <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="13" t="n"/>
       <c r="R22" s="13" t="n"/>
       <c r="S22" s="24" t="n"/>
     </row>
@@ -2250,6 +2290,7 @@
       <c r="N23" s="11" t="n"/>
       <c r="O23" s="11" t="n"/>
       <c r="P23" s="11" t="n"/>
+      <c r="Q23" s="9" t="n"/>
       <c r="R23" s="9" t="n"/>
       <c r="S23" s="22" t="n"/>
     </row>
@@ -2304,6 +2345,7 @@
       <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="n"/>
       <c r="P24" s="15" t="n"/>
+      <c r="Q24" s="13" t="n"/>
       <c r="R24" s="13" t="n"/>
       <c r="S24" s="24" t="n"/>
     </row>
@@ -2358,6 +2400,7 @@
       <c r="N25" s="11" t="n"/>
       <c r="O25" s="11" t="n"/>
       <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="9" t="n"/>
       <c r="R25" s="9" t="n"/>
       <c r="S25" s="22" t="n"/>
     </row>
@@ -2412,6 +2455,7 @@
       <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="n"/>
       <c r="P26" s="15" t="n"/>
+      <c r="Q26" s="13" t="n"/>
       <c r="R26" s="13" t="n"/>
       <c r="S26" s="24" t="n"/>
     </row>
@@ -2466,6 +2510,7 @@
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
       <c r="P27" s="11" t="n"/>
+      <c r="Q27" s="9" t="n"/>
       <c r="R27" s="9" t="n"/>
       <c r="S27" s="22" t="n"/>
     </row>
@@ -2486,6 +2531,7 @@
       <c r="N28" s="13" t="n"/>
       <c r="O28" s="13" t="n"/>
       <c r="P28" s="13" t="n"/>
+      <c r="Q28" s="13" t="n"/>
       <c r="R28" s="13" t="n"/>
       <c r="S28" s="24" t="n"/>
     </row>
@@ -2506,6 +2552,7 @@
       <c r="N29" s="9" t="n"/>
       <c r="O29" s="9" t="n"/>
       <c r="P29" s="9" t="n"/>
+      <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
       <c r="S29" s="22" t="n"/>
     </row>
@@ -2526,6 +2573,7 @@
       <c r="N30" s="13" t="n"/>
       <c r="O30" s="13" t="n"/>
       <c r="P30" s="13" t="n"/>
+      <c r="Q30" s="13" t="n"/>
       <c r="R30" s="13" t="n"/>
       <c r="S30" s="24" t="n"/>
     </row>
@@ -2546,6 +2594,7 @@
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="9" t="n"/>
       <c r="P31" s="9" t="n"/>
+      <c r="Q31" s="9" t="n"/>
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="22" t="n"/>
     </row>
@@ -2566,6 +2615,7 @@
       <c r="N32" s="13" t="n"/>
       <c r="O32" s="13" t="n"/>
       <c r="P32" s="13" t="n"/>
+      <c r="Q32" s="13" t="n"/>
       <c r="R32" s="13" t="n"/>
       <c r="S32" s="24" t="n"/>
     </row>
@@ -2586,6 +2636,7 @@
       <c r="N33" s="9" t="n"/>
       <c r="O33" s="9" t="n"/>
       <c r="P33" s="9" t="n"/>
+      <c r="Q33" s="9" t="n"/>
       <c r="R33" s="9" t="n"/>
       <c r="S33" s="22" t="n"/>
     </row>
@@ -2606,6 +2657,7 @@
       <c r="N34" s="13" t="n"/>
       <c r="O34" s="13" t="n"/>
       <c r="P34" s="13" t="n"/>
+      <c r="Q34" s="13" t="n"/>
       <c r="R34" s="13" t="n"/>
       <c r="S34" s="24" t="n"/>
     </row>
@@ -2626,6 +2678,7 @@
       <c r="N35" s="9" t="n"/>
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
+      <c r="Q35" s="9" t="n"/>
       <c r="R35" s="9" t="n"/>
       <c r="S35" s="22" t="n"/>
     </row>
@@ -2646,6 +2699,7 @@
       <c r="N36" s="13" t="n"/>
       <c r="O36" s="13" t="n"/>
       <c r="P36" s="13" t="n"/>
+      <c r="Q36" s="13" t="n"/>
       <c r="R36" s="13" t="n"/>
       <c r="S36" s="24" t="n"/>
     </row>
@@ -2666,6 +2720,7 @@
       <c r="N37" s="9" t="n"/>
       <c r="O37" s="9" t="n"/>
       <c r="P37" s="9" t="n"/>
+      <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="22" t="n"/>
     </row>
@@ -2686,6 +2741,7 @@
       <c r="N38" s="13" t="n"/>
       <c r="O38" s="13" t="n"/>
       <c r="P38" s="13" t="n"/>
+      <c r="Q38" s="13" t="n"/>
       <c r="R38" s="13" t="n"/>
       <c r="S38" s="24" t="n"/>
     </row>
@@ -2706,6 +2762,7 @@
       <c r="N39" s="9" t="n"/>
       <c r="O39" s="9" t="n"/>
       <c r="P39" s="9" t="n"/>
+      <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="22" t="n"/>
     </row>
@@ -2726,6 +2783,7 @@
       <c r="N40" s="13" t="n"/>
       <c r="O40" s="13" t="n"/>
       <c r="P40" s="13" t="n"/>
+      <c r="Q40" s="13" t="n"/>
       <c r="R40" s="13" t="n"/>
       <c r="S40" s="24" t="n"/>
     </row>
@@ -2746,6 +2804,7 @@
       <c r="N41" s="9" t="n"/>
       <c r="O41" s="9" t="n"/>
       <c r="P41" s="9" t="n"/>
+      <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="22" t="n"/>
     </row>
@@ -2766,6 +2825,7 @@
       <c r="N42" s="13" t="n"/>
       <c r="O42" s="13" t="n"/>
       <c r="P42" s="13" t="n"/>
+      <c r="Q42" s="13" t="n"/>
       <c r="R42" s="13" t="n"/>
       <c r="S42" s="24" t="n"/>
     </row>
@@ -2786,6 +2846,7 @@
       <c r="N43" s="9" t="n"/>
       <c r="O43" s="9" t="n"/>
       <c r="P43" s="9" t="n"/>
+      <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
       <c r="S43" s="22" t="n"/>
     </row>
@@ -2806,6 +2867,7 @@
       <c r="N44" s="13" t="n"/>
       <c r="O44" s="13" t="n"/>
       <c r="P44" s="13" t="n"/>
+      <c r="Q44" s="13" t="n"/>
       <c r="R44" s="13" t="n"/>
       <c r="S44" s="24" t="n"/>
     </row>
@@ -2826,6 +2888,7 @@
       <c r="N45" s="9" t="n"/>
       <c r="O45" s="9" t="n"/>
       <c r="P45" s="9" t="n"/>
+      <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
       <c r="S45" s="22" t="n"/>
     </row>
@@ -2846,6 +2909,7 @@
       <c r="N46" s="13" t="n"/>
       <c r="O46" s="13" t="n"/>
       <c r="P46" s="13" t="n"/>
+      <c r="Q46" s="13" t="n"/>
       <c r="R46" s="13" t="n"/>
       <c r="S46" s="24" t="n"/>
     </row>
@@ -2866,6 +2930,7 @@
       <c r="N47" s="9" t="n"/>
       <c r="O47" s="9" t="n"/>
       <c r="P47" s="9" t="n"/>
+      <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
       <c r="S47" s="22" t="n"/>
     </row>
@@ -2886,6 +2951,7 @@
       <c r="N48" s="13" t="n"/>
       <c r="O48" s="13" t="n"/>
       <c r="P48" s="13" t="n"/>
+      <c r="Q48" s="13" t="n"/>
       <c r="R48" s="13" t="n"/>
       <c r="S48" s="24" t="n"/>
     </row>
@@ -2906,6 +2972,7 @@
       <c r="N49" s="9" t="n"/>
       <c r="O49" s="9" t="n"/>
       <c r="P49" s="9" t="n"/>
+      <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="22" t="n"/>
     </row>
@@ -2926,6 +2993,7 @@
       <c r="N50" s="13" t="n"/>
       <c r="O50" s="13" t="n"/>
       <c r="P50" s="13" t="n"/>
+      <c r="Q50" s="13" t="n"/>
       <c r="R50" s="13" t="n"/>
       <c r="S50" s="24" t="n"/>
     </row>
@@ -2946,6 +3014,7 @@
       <c r="N51" s="9" t="n"/>
       <c r="O51" s="9" t="n"/>
       <c r="P51" s="9" t="n"/>
+      <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="22" t="n"/>
     </row>
@@ -2966,6 +3035,7 @@
       <c r="N52" s="13" t="n"/>
       <c r="O52" s="13" t="n"/>
       <c r="P52" s="13" t="n"/>
+      <c r="Q52" s="13" t="n"/>
       <c r="R52" s="13" t="n"/>
       <c r="S52" s="24" t="n"/>
     </row>
@@ -2986,6 +3056,7 @@
       <c r="N53" s="9" t="n"/>
       <c r="O53" s="9" t="n"/>
       <c r="P53" s="9" t="n"/>
+      <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
       <c r="S53" s="22" t="n"/>
     </row>
@@ -3006,6 +3077,7 @@
       <c r="N54" s="13" t="n"/>
       <c r="O54" s="13" t="n"/>
       <c r="P54" s="13" t="n"/>
+      <c r="Q54" s="13" t="n"/>
       <c r="R54" s="13" t="n"/>
       <c r="S54" s="24" t="n"/>
     </row>
@@ -3026,6 +3098,7 @@
       <c r="N55" s="9" t="n"/>
       <c r="O55" s="9" t="n"/>
       <c r="P55" s="9" t="n"/>
+      <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
       <c r="S55" s="22" t="n"/>
     </row>
@@ -3046,6 +3119,7 @@
       <c r="N56" s="13" t="n"/>
       <c r="O56" s="13" t="n"/>
       <c r="P56" s="13" t="n"/>
+      <c r="Q56" s="13" t="n"/>
       <c r="R56" s="13" t="n"/>
       <c r="S56" s="24" t="n"/>
     </row>
@@ -3066,14 +3140,15 @@
       <c r="N57" s="9" t="n"/>
       <c r="O57" s="9" t="n"/>
       <c r="P57" s="9" t="n"/>
+      <c r="Q57" s="9" t="n"/>
       <c r="R57" s="9" t="n"/>
       <c r="S57" s="22" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="Q5:Q28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -612,8 +630,11 @@
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당자
-(직접 입력)</t>
+        <t>▣ 부서 담당자
+• 부서 내 실제 담당자 이름 입력
+  예: 정민규, 한재운, 이찬
+• 입력 시: PMS에도 자동 반영
+• 빈 칸: 부서 참여 확정, 담당자 미정</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
@@ -627,51 +648,89 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOM작성
-(직접 입력)</t>
+        <t>▣ BOM작성 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 구매검토
-(직접 입력)</t>
+        <t>▣ 구매검토 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 구매품발주
-(직접 입력)</t>
+        <t>▣ 구매품발주 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공품발주
-(직접 입력)</t>
+        <t>▣ 가공품발주 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입고
-(직접 입력)</t>
+        <t>▣ 입고 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 외주
-입고일
-(직접 입력)</t>
+        <t>▣ 외주 입고일 (양산 외주발주)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD
+• 외부업체에서 양산 가공품이 실제 입고된 날짜
+• 비워두면: 대시보드 외주현황에 '진행중'
+• 입고일 입력 시: '입고완료' 자동 분류</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상태
-(직접 입력)</t>
+        <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모
-(직접 입력)</t>
+        <t>▣ 메모 (부서 자유 입력)
+• 자유 텍스트 입력
+• 활용:
+  - 이슈사항 (예: 자재 결품, 외주 지연)
+  - 변경 요청 (예: 사양 변경, 납기 조정)
+  - 다른 부서·PM에게 공유할 정보
+• 대시보드 집계에는 미포함</t>
       </text>
     </comment>
   </commentList>
@@ -993,7 +1052,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1018,7 +1077,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="68" t="inlineStr">
+      <c r="A2" s="75" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1040,9 +1099,9 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="69" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:45</t>
+      <c r="S2" s="76" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1052,7 +1061,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="74" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1077,7 +1086,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="75" t="inlineStr">
+      <c r="A2" s="78" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1099,9 +1108,9 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="76" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="S2" s="79" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:01</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -648,11 +657,15 @@
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+• 자동 계산 (수정 불가, sync 시 갱신)
+• 시작일·완료일 입력 기반:
+    0%  = 미착수    (시작일·완료일 모두 빈 칸)
+   50%  = 진행중    (시작일만 입력)
+  100%  = 완료      (완료일까지 입력)
+• ★ 이 값은 '이 부서'만의 진척률입니다.
+• 프로젝트 전체 진척률은 PMS 1_프로젝트등록
+  '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
@@ -1061,7 +1074,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="77" t="inlineStr">
+      <c r="A1" s="80" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1086,7 +1099,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1108,9 +1121,9 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="79" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:01</t>
+      <c r="S2" s="82" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:54</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1277,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>전체진척률(%)</t>
+          <t>부서진척률(%)</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -1355,7 +1368,7 @@
       </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="10" t="n">
-        <v>0.009166666666666667</v>
+        <v>0</v>
       </c>
       <c r="L5" s="11" t="n"/>
       <c r="M5" s="11" t="n"/>
@@ -1412,7 +1425,7 @@
       </c>
       <c r="J6" s="13" t="n"/>
       <c r="K6" s="14" t="n">
-        <v>0.007800000000000001</v>
+        <v>0</v>
       </c>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
@@ -1468,7 +1481,9 @@
         </is>
       </c>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
@@ -1523,7 +1538,9 @@
         </is>
       </c>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15" t="n"/>
       <c r="N8" s="15" t="n"/>
@@ -1578,7 +1595,9 @@
         </is>
       </c>
       <c r="J9" s="9" t="n"/>
-      <c r="K9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="11" t="n"/>
       <c r="M9" s="11" t="n"/>
       <c r="N9" s="11" t="n"/>
@@ -1633,7 +1652,9 @@
         </is>
       </c>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
       <c r="N10" s="15" t="n"/>
@@ -1688,7 +1709,9 @@
         </is>
       </c>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
@@ -1743,7 +1766,9 @@
         </is>
       </c>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
       <c r="N12" s="15" t="n"/>
@@ -1798,7 +1823,9 @@
         </is>
       </c>
       <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="11" t="n"/>
       <c r="M13" s="11" t="n"/>
       <c r="N13" s="11" t="n"/>
@@ -1853,7 +1880,9 @@
         </is>
       </c>
       <c r="J14" s="13" t="n"/>
-      <c r="K14" s="14" t="inlineStr"/>
+      <c r="K14" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
       <c r="N14" s="15" t="n"/>
@@ -1908,7 +1937,9 @@
         </is>
       </c>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="11" t="n"/>
@@ -1964,7 +1995,7 @@
       </c>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="14" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
@@ -2021,7 +2052,7 @@
       </c>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="11" t="n"/>
@@ -2077,7 +2108,9 @@
         </is>
       </c>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -2132,7 +2165,9 @@
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="10" t="inlineStr"/>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" s="11" t="n"/>
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="11" t="n"/>
@@ -2187,7 +2222,9 @@
         </is>
       </c>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
@@ -2242,7 +2279,9 @@
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="11" t="n"/>
       <c r="M21" s="11" t="n"/>
       <c r="N21" s="11" t="n"/>
@@ -2297,7 +2336,9 @@
         </is>
       </c>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
@@ -2352,7 +2393,9 @@
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
-      <c r="K23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L23" s="11" t="n"/>
       <c r="M23" s="11" t="n"/>
       <c r="N23" s="11" t="n"/>
@@ -2407,7 +2450,9 @@
         </is>
       </c>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="14" t="inlineStr"/>
+      <c r="K24" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
       <c r="N24" s="15" t="n"/>
@@ -2462,7 +2507,9 @@
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L25" s="11" t="n"/>
       <c r="M25" s="11" t="n"/>
       <c r="N25" s="11" t="n"/>
@@ -2517,7 +2564,9 @@
         </is>
       </c>
       <c r="J26" s="13" t="n"/>
-      <c r="K26" s="14" t="inlineStr"/>
+      <c r="K26" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
       <c r="N26" s="15" t="n"/>
@@ -2572,7 +2621,9 @@
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -421,6 +421,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -542,15 +560,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -564,46 +597,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -614,11 +687,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -633,31 +714,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -666,93 +771,158 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOM작성 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOM작성 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 구매검토 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 구매검토 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 구매품발주 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 구매품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공품발주 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입고 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입고 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
 • 0 또는 빈 칸 = 미착수
 • 부서장·담당자가 매주 진척률 갱신
 • 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 외주 입고일 (양산 외주발주)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 외주 입고일 (양산 외주발주)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 외부업체에서 양산 가공품이 실제 입고된 날짜
 • 비워두면: 대시보드 외주현황에 '진행중'
 • 입고일 입력 시: '입고완료' 자동 분류</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1074,7 +1244,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="80" t="inlineStr">
+      <c r="A1" s="86" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1099,7 +1269,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="87" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1121,9 +1291,9 @@
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="16" t="n"/>
       <c r="R2" s="17" t="n"/>
-      <c r="S2" s="82" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:54</t>
+      <c r="S2" s="88" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:34</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -124,7 +124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -204,11 +204,40 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -476,6 +505,17 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1244,7 +1284,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="86" t="inlineStr">
+      <c r="A1" s="89" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1269,7 +1309,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="87" t="inlineStr">
+      <c r="A2" s="90" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1288,14 +1328,14 @@
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
-      <c r="P2" s="16" t="n"/>
-      <c r="Q2" s="16" t="n"/>
-      <c r="R2" s="17" t="n"/>
-      <c r="S2" s="88" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:34</t>
-        </is>
-      </c>
+      <c r="P2" s="17" t="n"/>
+      <c r="Q2" s="91" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:56</t>
+        </is>
+      </c>
+      <c r="R2" s="92" t="n"/>
+      <c r="S2" s="93" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -3435,9 +3475,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
+  <mergeCells count="3">
+    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="Q5:Q28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -600,30 +609,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -637,86 +631,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -727,19 +681,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -754,55 +700,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -811,158 +733,118 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ BOM작성 (세부항목 진척률)
+        <t>▣ BOM작성 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 구매검토 (세부항목 진척률)
+        <t>▣ 구매검토 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 구매품발주 (세부항목 진척률)
+        <t>▣ 구매품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 가공품발주 (세부항목 진척률)
+        <t>▣ 가공품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입고 (세부항목 진척률)
+        <t>▣ 입고 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-        </r>
+• 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
+  또는 0~100 정수도 허용 (예: 50, 100)
+📋 입력값 의미:
+  ▸ 빈 칸  → ⭕ '해당없음' (이 세부항목은 본 프로젝트 무관)
+           — 부서 진척률 평균에서 ★분모 제외★
+  ▸ 0     → 미착수 (분모에 포함, 0%로 계산)
+  ▸ 0.5   → 50% 진행 중
+  ▸ 1.0   → 100% 완료
+💡 부서장·담당자가 매주 진척률 갱신
+💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 외주 입고일 (양산 외주발주)
+        <t>▣ 외주 입고일 (양산 외주발주)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 외부업체에서 양산 가공품이 실제 입고된 날짜
 • 비워두면: 대시보드 외주현황에 '진행중'
 • 입고일 입력 시: '입고완료' 자동 분류</t>
-        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1273,18 +1155,18 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="55" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" style="55" min="12" max="12"/>
-    <col width="10" customWidth="1" style="55" min="13" max="13"/>
-    <col width="12" customWidth="1" style="55" min="14" max="14"/>
-    <col width="12" customWidth="1" style="55" min="15" max="15"/>
-    <col width="6" customWidth="1" style="55" min="16" max="16"/>
-    <col width="12" customWidth="1" style="55" min="17" max="17"/>
+    <col width="5" customWidth="1" style="55" min="12" max="12"/>
+    <col width="5" customWidth="1" style="55" min="13" max="13"/>
+    <col width="5" customWidth="1" style="55" min="14" max="14"/>
+    <col width="5" customWidth="1" style="55" min="15" max="15"/>
+    <col width="5" customWidth="1" style="55" min="16" max="16"/>
+    <col width="5" customWidth="1" style="55" min="17" max="17"/>
     <col width="10" customWidth="1" style="55" min="18" max="18"/>
     <col width="28" customWidth="1" style="55" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="89" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1309,7 +1191,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="90" t="inlineStr">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1329,13 +1211,13 @@
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="17" t="n"/>
-      <c r="Q2" s="91" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:56</t>
-        </is>
-      </c>
-      <c r="R2" s="92" t="n"/>
-      <c r="S2" s="93" t="n"/>
+      <c r="Q2" s="96" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:27</t>
+        </is>
+      </c>
+      <c r="R2" s="16" t="n"/>
+      <c r="S2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1492,22 +1374,26 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>BOM작성</t>
+          <t>BOM
+작성</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>구매검토</t>
+          <t>구매검
+토</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>구매품발주</t>
+          <t>구매품
+발주</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>가공품발주</t>
+          <t>가공품
+발주</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -1577,8 +1463,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n"/>
-      <c r="K5" s="10" t="n">
-        <v>0</v>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L5" s="11" t="n"/>
       <c r="M5" s="11" t="n"/>
@@ -1634,8 +1522,10 @@
         </is>
       </c>
       <c r="J6" s="13" t="n"/>
-      <c r="K6" s="14" t="n">
-        <v>0</v>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
@@ -1691,8 +1581,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="10" t="n">
-        <v>0</v>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
@@ -1748,8 +1640,10 @@
         </is>
       </c>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14" t="n">
-        <v>0</v>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15" t="n"/>
@@ -1805,8 +1699,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n"/>
-      <c r="K9" s="10" t="n">
-        <v>0</v>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L9" s="11" t="n"/>
       <c r="M9" s="11" t="n"/>
@@ -1862,8 +1758,10 @@
         </is>
       </c>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="14" t="n">
-        <v>0</v>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
@@ -1919,8 +1817,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10" t="n">
-        <v>0</v>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
@@ -1976,8 +1876,10 @@
         </is>
       </c>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="14" t="n">
-        <v>0</v>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -2033,8 +1935,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L13" s="11" t="n"/>
       <c r="M13" s="11" t="n"/>
@@ -2090,8 +1994,10 @@
         </is>
       </c>
       <c r="J14" s="13" t="n"/>
-      <c r="K14" s="14" t="n">
-        <v>0</v>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -2147,8 +2053,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="10" t="n">
-        <v>0</v>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L15" s="11" t="n"/>
       <c r="M15" s="11" t="n"/>
@@ -2204,8 +2112,10 @@
         </is>
       </c>
       <c r="J16" s="13" t="n"/>
-      <c r="K16" s="14" t="n">
-        <v>0</v>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
@@ -2261,8 +2171,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n"/>
-      <c r="K17" s="10" t="n">
-        <v>0</v>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L17" s="11" t="n"/>
       <c r="M17" s="11" t="n"/>
@@ -2318,8 +2230,10 @@
         </is>
       </c>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="14" t="n">
-        <v>0</v>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
@@ -2375,8 +2289,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="10" t="n">
-        <v>0</v>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L19" s="11" t="n"/>
       <c r="M19" s="11" t="n"/>
@@ -2432,8 +2348,10 @@
         </is>
       </c>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="14" t="n">
-        <v>0</v>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
@@ -2489,8 +2407,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="10" t="n">
-        <v>0</v>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L21" s="11" t="n"/>
       <c r="M21" s="11" t="n"/>
@@ -2546,8 +2466,10 @@
         </is>
       </c>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="14" t="n">
-        <v>0</v>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
@@ -2603,8 +2525,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
-      <c r="K23" s="10" t="n">
-        <v>0</v>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L23" s="11" t="n"/>
       <c r="M23" s="11" t="n"/>
@@ -2660,8 +2584,10 @@
         </is>
       </c>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="14" t="n">
-        <v>0</v>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
@@ -2717,8 +2643,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="n">
-        <v>0</v>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L25" s="11" t="n"/>
       <c r="M25" s="11" t="n"/>
@@ -2774,8 +2702,10 @@
         </is>
       </c>
       <c r="J26" s="13" t="n"/>
-      <c r="K26" s="14" t="n">
-        <v>0</v>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
@@ -2831,8 +2761,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="10" t="n">
-        <v>0</v>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="11" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -609,15 +618,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -631,46 +655,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -681,11 +745,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -700,31 +772,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -733,11 +829,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOM작성 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOM작성 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -749,11 +853,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 구매검토 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 구매검토 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -765,11 +877,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 구매품발주 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 구매품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -781,11 +901,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공품발주 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -797,11 +925,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입고 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입고 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -813,38 +949,63 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 외주 입고일 (양산 외주발주)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 외주 입고일 (양산 외주발주)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 외부업체에서 양산 가공품이 실제 입고된 날짜
 • 비워두면: 대시보드 외주현황에 '진행중'
 • 입고일 입력 시: '입고완료' 자동 분류</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1155,18 +1316,18 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="55" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" style="55" min="12" max="12"/>
-    <col width="5" customWidth="1" style="55" min="13" max="13"/>
-    <col width="5" customWidth="1" style="55" min="14" max="14"/>
-    <col width="5" customWidth="1" style="55" min="15" max="15"/>
-    <col width="5" customWidth="1" style="55" min="16" max="16"/>
-    <col width="5" customWidth="1" style="55" min="17" max="17"/>
+    <col width="7" customWidth="1" style="55" min="12" max="12"/>
+    <col width="7" customWidth="1" style="55" min="13" max="13"/>
+    <col width="7" customWidth="1" style="55" min="14" max="14"/>
+    <col width="7" customWidth="1" style="55" min="15" max="15"/>
+    <col width="7" customWidth="1" style="55" min="16" max="16"/>
+    <col width="7" customWidth="1" style="55" min="17" max="17"/>
     <col width="10" customWidth="1" style="55" min="18" max="18"/>
     <col width="28" customWidth="1" style="55" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="94" t="inlineStr">
+      <c r="A1" s="97" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1191,7 +1352,7 @@
       <c r="S1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="95" t="inlineStr">
+      <c r="A2" s="98" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1211,9 +1372,9 @@
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="17" t="n"/>
-      <c r="Q2" s="96" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:27</t>
+      <c r="Q2" s="99" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:39</t>
         </is>
       </c>
       <c r="R2" s="16" t="n"/>
@@ -1380,8 +1541,8 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>구매검
-토</t>
+          <t>구매
+검토</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -618,30 +627,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -655,86 +649,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -745,19 +699,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -772,55 +718,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -829,19 +751,11 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ BOM작성 (세부항목 진척률)
+        <t>▣ BOM작성 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -853,19 +767,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 구매검토 (세부항목 진척률)
+        <t>▣ 구매검토 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -877,19 +783,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 구매품발주 (세부항목 진척률)
+        <t>▣ 구매품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -901,19 +799,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 가공품발주 (세부항목 진척률)
+        <t>▣ 가공품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -925,19 +815,11 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 입고 (세부항목 진척률)
+        <t>▣ 입고 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -949,63 +831,51 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
-        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 외주 입고일 (양산 외주발주)
+        <t>▣ 외주 입고예정일 (외주 발주 후 예정)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 외주(자재·양산 가공품) 발주 시
+  외부업체와 약속한 ★입고 완료 예정일★ 기입
+📋 운영:
+  ▸ 발주 시 예정일 입력
+  ▸ 실제 입고일과 비교 → 지연 여부 추적
+  ▸ 비워두면: 미발주 또는 일정 미정</t>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0" shapeId="0">
+      <text>
+        <t>▣ 외주 입고일 (양산 외주발주)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 외부업체에서 양산 가공품이 실제 입고된 날짜
 • 비워두면: 대시보드 외주현황에 '진행중'
 • 입고일 입력 시: '입고완료' 자동 분류</t>
-        </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1302,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:T57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1322,12 +1192,13 @@
     <col width="7" customWidth="1" style="55" min="15" max="15"/>
     <col width="7" customWidth="1" style="55" min="16" max="16"/>
     <col width="7" customWidth="1" style="55" min="17" max="17"/>
-    <col width="10" customWidth="1" style="55" min="18" max="18"/>
-    <col width="28" customWidth="1" style="55" min="19" max="19"/>
+    <col width="7" customWidth="1" style="55" min="18" max="18"/>
+    <col width="10" customWidth="1" style="55" min="19" max="19"/>
+    <col width="28" customWidth="1" style="55" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="97" t="inlineStr">
+      <c r="A1" s="100" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1349,10 +1220,11 @@
       <c r="P1" s="16" t="n"/>
       <c r="Q1" s="16" t="n"/>
       <c r="R1" s="16" t="n"/>
-      <c r="S1" s="17" t="n"/>
+      <c r="S1" s="16" t="n"/>
+      <c r="T1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1371,14 +1243,15 @@
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
-      <c r="P2" s="17" t="n"/>
-      <c r="Q2" s="99" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:39</t>
-        </is>
-      </c>
-      <c r="R2" s="16" t="n"/>
-      <c r="S2" s="17" t="n"/>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="17" t="n"/>
+      <c r="R2" s="102" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:47</t>
+        </is>
+      </c>
+      <c r="S2" s="16" t="n"/>
+      <c r="T2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1466,12 +1339,17 @@
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1565,15 +1443,21 @@
       <c r="Q4" s="70" t="inlineStr">
         <is>
           <t>외주
+예정일</t>
+        </is>
+      </c>
+      <c r="R4" s="70" t="inlineStr">
+        <is>
+          <t>외주
 입고일</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1636,7 +1520,8 @@
       <c r="P5" s="11" t="n"/>
       <c r="Q5" s="9" t="n"/>
       <c r="R5" s="9" t="n"/>
-      <c r="S5" s="22" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1695,7 +1580,8 @@
       <c r="P6" s="15" t="n"/>
       <c r="Q6" s="13" t="n"/>
       <c r="R6" s="13" t="n"/>
-      <c r="S6" s="24" t="n"/>
+      <c r="S6" s="13" t="n"/>
+      <c r="T6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1754,7 +1640,8 @@
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="9" t="n"/>
       <c r="R7" s="9" t="n"/>
-      <c r="S7" s="22" t="n"/>
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1813,7 +1700,8 @@
       <c r="P8" s="15" t="n"/>
       <c r="Q8" s="13" t="n"/>
       <c r="R8" s="13" t="n"/>
-      <c r="S8" s="24" t="n"/>
+      <c r="S8" s="13" t="n"/>
+      <c r="T8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1872,7 +1760,8 @@
       <c r="P9" s="11" t="n"/>
       <c r="Q9" s="9" t="n"/>
       <c r="R9" s="9" t="n"/>
-      <c r="S9" s="22" t="n"/>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1931,7 +1820,8 @@
       <c r="P10" s="15" t="n"/>
       <c r="Q10" s="13" t="n"/>
       <c r="R10" s="13" t="n"/>
-      <c r="S10" s="24" t="n"/>
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1990,7 +1880,8 @@
       <c r="P11" s="11" t="n"/>
       <c r="Q11" s="9" t="n"/>
       <c r="R11" s="9" t="n"/>
-      <c r="S11" s="22" t="n"/>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -2049,7 +1940,8 @@
       <c r="P12" s="15" t="n"/>
       <c r="Q12" s="13" t="n"/>
       <c r="R12" s="13" t="n"/>
-      <c r="S12" s="24" t="n"/>
+      <c r="S12" s="13" t="n"/>
+      <c r="T12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -2108,7 +2000,8 @@
       <c r="P13" s="11" t="n"/>
       <c r="Q13" s="9" t="n"/>
       <c r="R13" s="9" t="n"/>
-      <c r="S13" s="22" t="n"/>
+      <c r="S13" s="9" t="n"/>
+      <c r="T13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -2167,7 +2060,8 @@
       <c r="P14" s="15" t="n"/>
       <c r="Q14" s="13" t="n"/>
       <c r="R14" s="13" t="n"/>
-      <c r="S14" s="24" t="n"/>
+      <c r="S14" s="13" t="n"/>
+      <c r="T14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -2226,7 +2120,8 @@
       <c r="P15" s="11" t="n"/>
       <c r="Q15" s="9" t="n"/>
       <c r="R15" s="9" t="n"/>
-      <c r="S15" s="22" t="n"/>
+      <c r="S15" s="9" t="n"/>
+      <c r="T15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -2285,7 +2180,8 @@
       <c r="P16" s="15" t="n"/>
       <c r="Q16" s="13" t="n"/>
       <c r="R16" s="13" t="n"/>
-      <c r="S16" s="24" t="n"/>
+      <c r="S16" s="13" t="n"/>
+      <c r="T16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -2344,7 +2240,8 @@
       <c r="P17" s="11" t="n"/>
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
-      <c r="S17" s="22" t="n"/>
+      <c r="S17" s="9" t="n"/>
+      <c r="T17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -2403,7 +2300,8 @@
       <c r="P18" s="15" t="n"/>
       <c r="Q18" s="13" t="n"/>
       <c r="R18" s="13" t="n"/>
-      <c r="S18" s="24" t="n"/>
+      <c r="S18" s="13" t="n"/>
+      <c r="T18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2462,7 +2360,8 @@
       <c r="P19" s="11" t="n"/>
       <c r="Q19" s="9" t="n"/>
       <c r="R19" s="9" t="n"/>
-      <c r="S19" s="22" t="n"/>
+      <c r="S19" s="9" t="n"/>
+      <c r="T19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2521,7 +2420,8 @@
       <c r="P20" s="15" t="n"/>
       <c r="Q20" s="13" t="n"/>
       <c r="R20" s="13" t="n"/>
-      <c r="S20" s="24" t="n"/>
+      <c r="S20" s="13" t="n"/>
+      <c r="T20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2580,7 +2480,8 @@
       <c r="P21" s="11" t="n"/>
       <c r="Q21" s="9" t="n"/>
       <c r="R21" s="9" t="n"/>
-      <c r="S21" s="22" t="n"/>
+      <c r="S21" s="9" t="n"/>
+      <c r="T21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2639,7 +2540,8 @@
       <c r="P22" s="15" t="n"/>
       <c r="Q22" s="13" t="n"/>
       <c r="R22" s="13" t="n"/>
-      <c r="S22" s="24" t="n"/>
+      <c r="S22" s="13" t="n"/>
+      <c r="T22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2698,7 +2600,8 @@
       <c r="P23" s="11" t="n"/>
       <c r="Q23" s="9" t="n"/>
       <c r="R23" s="9" t="n"/>
-      <c r="S23" s="22" t="n"/>
+      <c r="S23" s="9" t="n"/>
+      <c r="T23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2757,7 +2660,8 @@
       <c r="P24" s="15" t="n"/>
       <c r="Q24" s="13" t="n"/>
       <c r="R24" s="13" t="n"/>
-      <c r="S24" s="24" t="n"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2816,7 +2720,8 @@
       <c r="P25" s="11" t="n"/>
       <c r="Q25" s="9" t="n"/>
       <c r="R25" s="9" t="n"/>
-      <c r="S25" s="22" t="n"/>
+      <c r="S25" s="9" t="n"/>
+      <c r="T25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2875,7 +2780,8 @@
       <c r="P26" s="15" t="n"/>
       <c r="Q26" s="13" t="n"/>
       <c r="R26" s="13" t="n"/>
-      <c r="S26" s="24" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2934,7 +2840,8 @@
       <c r="P27" s="11" t="n"/>
       <c r="Q27" s="9" t="n"/>
       <c r="R27" s="9" t="n"/>
-      <c r="S27" s="22" t="n"/>
+      <c r="S27" s="9" t="n"/>
+      <c r="T27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n"/>
@@ -2955,7 +2862,8 @@
       <c r="P28" s="13" t="n"/>
       <c r="Q28" s="13" t="n"/>
       <c r="R28" s="13" t="n"/>
-      <c r="S28" s="24" t="n"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n"/>
@@ -2976,7 +2884,8 @@
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
-      <c r="S29" s="22" t="n"/>
+      <c r="S29" s="9" t="n"/>
+      <c r="T29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n"/>
@@ -2997,7 +2906,8 @@
       <c r="P30" s="13" t="n"/>
       <c r="Q30" s="13" t="n"/>
       <c r="R30" s="13" t="n"/>
-      <c r="S30" s="24" t="n"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n"/>
@@ -3018,7 +2928,8 @@
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n"/>
       <c r="R31" s="9" t="n"/>
-      <c r="S31" s="22" t="n"/>
+      <c r="S31" s="9" t="n"/>
+      <c r="T31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n"/>
@@ -3039,7 +2950,8 @@
       <c r="P32" s="13" t="n"/>
       <c r="Q32" s="13" t="n"/>
       <c r="R32" s="13" t="n"/>
-      <c r="S32" s="24" t="n"/>
+      <c r="S32" s="13" t="n"/>
+      <c r="T32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n"/>
@@ -3060,7 +2972,8 @@
       <c r="P33" s="9" t="n"/>
       <c r="Q33" s="9" t="n"/>
       <c r="R33" s="9" t="n"/>
-      <c r="S33" s="22" t="n"/>
+      <c r="S33" s="9" t="n"/>
+      <c r="T33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n"/>
@@ -3081,7 +2994,8 @@
       <c r="P34" s="13" t="n"/>
       <c r="Q34" s="13" t="n"/>
       <c r="R34" s="13" t="n"/>
-      <c r="S34" s="24" t="n"/>
+      <c r="S34" s="13" t="n"/>
+      <c r="T34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n"/>
@@ -3102,7 +3016,8 @@
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
       <c r="R35" s="9" t="n"/>
-      <c r="S35" s="22" t="n"/>
+      <c r="S35" s="9" t="n"/>
+      <c r="T35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n"/>
@@ -3123,7 +3038,8 @@
       <c r="P36" s="13" t="n"/>
       <c r="Q36" s="13" t="n"/>
       <c r="R36" s="13" t="n"/>
-      <c r="S36" s="24" t="n"/>
+      <c r="S36" s="13" t="n"/>
+      <c r="T36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n"/>
@@ -3144,7 +3060,8 @@
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
-      <c r="S37" s="22" t="n"/>
+      <c r="S37" s="9" t="n"/>
+      <c r="T37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n"/>
@@ -3165,7 +3082,8 @@
       <c r="P38" s="13" t="n"/>
       <c r="Q38" s="13" t="n"/>
       <c r="R38" s="13" t="n"/>
-      <c r="S38" s="24" t="n"/>
+      <c r="S38" s="13" t="n"/>
+      <c r="T38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n"/>
@@ -3186,7 +3104,8 @@
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
-      <c r="S39" s="22" t="n"/>
+      <c r="S39" s="9" t="n"/>
+      <c r="T39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n"/>
@@ -3207,7 +3126,8 @@
       <c r="P40" s="13" t="n"/>
       <c r="Q40" s="13" t="n"/>
       <c r="R40" s="13" t="n"/>
-      <c r="S40" s="24" t="n"/>
+      <c r="S40" s="13" t="n"/>
+      <c r="T40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n"/>
@@ -3228,7 +3148,8 @@
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
-      <c r="S41" s="22" t="n"/>
+      <c r="S41" s="9" t="n"/>
+      <c r="T41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n"/>
@@ -3249,7 +3170,8 @@
       <c r="P42" s="13" t="n"/>
       <c r="Q42" s="13" t="n"/>
       <c r="R42" s="13" t="n"/>
-      <c r="S42" s="24" t="n"/>
+      <c r="S42" s="13" t="n"/>
+      <c r="T42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n"/>
@@ -3270,7 +3192,8 @@
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
-      <c r="S43" s="22" t="n"/>
+      <c r="S43" s="9" t="n"/>
+      <c r="T43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n"/>
@@ -3291,7 +3214,8 @@
       <c r="P44" s="13" t="n"/>
       <c r="Q44" s="13" t="n"/>
       <c r="R44" s="13" t="n"/>
-      <c r="S44" s="24" t="n"/>
+      <c r="S44" s="13" t="n"/>
+      <c r="T44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n"/>
@@ -3312,7 +3236,8 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
-      <c r="S45" s="22" t="n"/>
+      <c r="S45" s="9" t="n"/>
+      <c r="T45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n"/>
@@ -3333,7 +3258,8 @@
       <c r="P46" s="13" t="n"/>
       <c r="Q46" s="13" t="n"/>
       <c r="R46" s="13" t="n"/>
-      <c r="S46" s="24" t="n"/>
+      <c r="S46" s="13" t="n"/>
+      <c r="T46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n"/>
@@ -3354,7 +3280,8 @@
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
-      <c r="S47" s="22" t="n"/>
+      <c r="S47" s="9" t="n"/>
+      <c r="T47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n"/>
@@ -3375,7 +3302,8 @@
       <c r="P48" s="13" t="n"/>
       <c r="Q48" s="13" t="n"/>
       <c r="R48" s="13" t="n"/>
-      <c r="S48" s="24" t="n"/>
+      <c r="S48" s="13" t="n"/>
+      <c r="T48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n"/>
@@ -3396,7 +3324,8 @@
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
-      <c r="S49" s="22" t="n"/>
+      <c r="S49" s="9" t="n"/>
+      <c r="T49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n"/>
@@ -3417,7 +3346,8 @@
       <c r="P50" s="13" t="n"/>
       <c r="Q50" s="13" t="n"/>
       <c r="R50" s="13" t="n"/>
-      <c r="S50" s="24" t="n"/>
+      <c r="S50" s="13" t="n"/>
+      <c r="T50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n"/>
@@ -3438,7 +3368,8 @@
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
-      <c r="S51" s="22" t="n"/>
+      <c r="S51" s="9" t="n"/>
+      <c r="T51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n"/>
@@ -3459,7 +3390,8 @@
       <c r="P52" s="13" t="n"/>
       <c r="Q52" s="13" t="n"/>
       <c r="R52" s="13" t="n"/>
-      <c r="S52" s="24" t="n"/>
+      <c r="S52" s="13" t="n"/>
+      <c r="T52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n"/>
@@ -3480,7 +3412,8 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="22" t="n"/>
+      <c r="S53" s="9" t="n"/>
+      <c r="T53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n"/>
@@ -3501,7 +3434,8 @@
       <c r="P54" s="13" t="n"/>
       <c r="Q54" s="13" t="n"/>
       <c r="R54" s="13" t="n"/>
-      <c r="S54" s="24" t="n"/>
+      <c r="S54" s="13" t="n"/>
+      <c r="T54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n"/>
@@ -3522,7 +3456,8 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="22" t="n"/>
+      <c r="S55" s="9" t="n"/>
+      <c r="T55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n"/>
@@ -3543,7 +3478,8 @@
       <c r="P56" s="13" t="n"/>
       <c r="Q56" s="13" t="n"/>
       <c r="R56" s="13" t="n"/>
-      <c r="S56" s="24" t="n"/>
+      <c r="S56" s="13" t="n"/>
+      <c r="T56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n"/>
@@ -3564,14 +3500,15 @@
       <c r="P57" s="9" t="n"/>
       <c r="Q57" s="9" t="n"/>
       <c r="R57" s="9" t="n"/>
-      <c r="S57" s="22" t="n"/>
+      <c r="S57" s="9" t="n"/>
+      <c r="T57" s="22" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="3">
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="R2:T2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="Q5:Q28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -627,15 +636,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -649,46 +673,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -699,11 +763,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -718,31 +790,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -751,11 +847,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOM작성 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ BOM작성 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -767,11 +871,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 구매검토 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 구매검토 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -783,11 +895,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 구매품발주 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 구매품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -799,11 +919,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 가공품발주 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공품발주 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -815,11 +943,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입고 (세부항목 진척률)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입고 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
   또는 0~100 정수도 허용 (예: 50, 100)
@@ -831,11 +967,19 @@
   ▸ 1.0   → 100% 완료
 💡 부서장·담당자가 매주 진척률 갱신
 💡 부서진척률(%)은 해당있는 세부항목 평균으로 자동 계산</t>
+        </r>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 외주 입고예정일 (외주 발주 후 예정)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 외주 입고예정일 (외주 발주 후 예정)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-07-15
 • 외주(자재·양산 가공품) 발주 시
@@ -844,38 +988,63 @@
   ▸ 발주 시 예정일 입력
   ▸ 실제 입고일과 비교 → 지연 여부 추적
   ▸ 비워두면: 미발주 또는 일정 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 외주 입고일 (양산 외주발주)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 외주 입고일 (양산 외주발주)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 외부업체에서 양산 가공품이 실제 입고된 날짜
 • 비워두면: 대시보드 외주현황에 '진행중'
 • 입고일 입력 시: '입고완료' 자동 분류</t>
+        </r>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1198,7 +1367,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="100" t="inlineStr">
+      <c r="A1" s="103" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1224,7 +1393,7 @@
       <c r="T1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="101" t="inlineStr">
+      <c r="A2" s="104" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1245,9 +1414,9 @@
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="17" t="n"/>
-      <c r="R2" s="102" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:47</t>
+      <c r="R2" s="105" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:00</t>
         </is>
       </c>
       <c r="S2" s="16" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -516,6 +516,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -883,6 +901,28 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
+          <t>▣ BOM작성 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• BOM작성 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = BOM작성 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
           <t>▣ 구매검토 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력 (예: 0.5 = 50%, 1.0 = 100%)
@@ -898,7 +938,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 구매검토 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 구매검토 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 구매검토 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -922,7 +984,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 구매품발주 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 구매품발주 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 구매품발주 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -946,7 +1030,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 가공품발주 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 가공품발주 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 가공품발주 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -970,7 +1076,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 입고 — 완료 예정일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 입고 작업의 ★완료 예정일★ 기입
+📋 운영:
+  ▸ 좌측 셀 = 진척률(%)
+  ▸ 이 셀  = 입고 완료 목표일
+  ▸ 진척률과 비교 → 일정 대비 진행도 추적
+  ▸ 예: 7/15까지 100% 목표인데 7/10 현재 50% → 일정 빠름
+• 비워두면: 일정 미정 또는 해당없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -991,7 +1119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="W4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1009,7 +1137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="X4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1028,7 +1156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="Y4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1341,7 +1469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T57"/>
+  <dimension ref="A1:Y57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1362,12 +1490,17 @@
     <col width="7" customWidth="1" style="55" min="16" max="16"/>
     <col width="7" customWidth="1" style="55" min="17" max="17"/>
     <col width="7" customWidth="1" style="55" min="18" max="18"/>
-    <col width="10" customWidth="1" style="55" min="19" max="19"/>
-    <col width="28" customWidth="1" style="55" min="20" max="20"/>
+    <col width="7" customWidth="1" style="55" min="19" max="19"/>
+    <col width="7" customWidth="1" style="55" min="20" max="20"/>
+    <col width="7" customWidth="1" style="55" min="21" max="21"/>
+    <col width="7" customWidth="1" style="55" min="22" max="22"/>
+    <col width="7" customWidth="1" style="55" min="23" max="23"/>
+    <col width="10" customWidth="1" style="55" min="24" max="24"/>
+    <col width="28" customWidth="1" style="55" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="103" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1390,10 +1523,15 @@
       <c r="Q1" s="16" t="n"/>
       <c r="R1" s="16" t="n"/>
       <c r="S1" s="16" t="n"/>
-      <c r="T1" s="17" t="n"/>
+      <c r="T1" s="16" t="n"/>
+      <c r="U1" s="16" t="n"/>
+      <c r="V1" s="16" t="n"/>
+      <c r="W1" s="16" t="n"/>
+      <c r="X1" s="16" t="n"/>
+      <c r="Y1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="104" t="inlineStr">
+      <c r="A2" s="110" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1413,14 +1551,19 @@
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="16" t="n"/>
-      <c r="Q2" s="17" t="n"/>
-      <c r="R2" s="105" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:00</t>
-        </is>
-      </c>
+      <c r="Q2" s="16" t="n"/>
+      <c r="R2" s="16" t="n"/>
       <c r="S2" s="16" t="n"/>
-      <c r="T2" s="17" t="n"/>
+      <c r="T2" s="16" t="n"/>
+      <c r="U2" s="16" t="n"/>
+      <c r="V2" s="17" t="n"/>
+      <c r="W2" s="111" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 14:35</t>
+        </is>
+      </c>
+      <c r="X2" s="16" t="n"/>
+      <c r="Y2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1483,42 +1626,67 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>✏입력</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1586,47 +1754,72 @@
 작성</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>구매
 검토</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="O4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>구매품
 발주</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="Q4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>가공품
 발주</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="S4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>입고</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="inlineStr">
+      <c r="U4" s="70" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="V4" s="70" t="inlineStr">
         <is>
           <t>외주
 예정일</t>
         </is>
       </c>
-      <c r="R4" s="70" t="inlineStr">
+      <c r="W4" s="70" t="inlineStr">
         <is>
           <t>외주
 입고일</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="X4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="T4" s="7" t="inlineStr">
+      <c r="Y4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1690,7 +1883,12 @@
       <c r="Q5" s="9" t="n"/>
       <c r="R5" s="9" t="n"/>
       <c r="S5" s="9" t="n"/>
-      <c r="T5" s="22" t="n"/>
+      <c r="T5" s="9" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="9" t="n"/>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1750,7 +1948,12 @@
       <c r="Q6" s="13" t="n"/>
       <c r="R6" s="13" t="n"/>
       <c r="S6" s="13" t="n"/>
-      <c r="T6" s="24" t="n"/>
+      <c r="T6" s="13" t="n"/>
+      <c r="U6" s="13" t="n"/>
+      <c r="V6" s="13" t="n"/>
+      <c r="W6" s="13" t="n"/>
+      <c r="X6" s="13" t="n"/>
+      <c r="Y6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1810,7 +2013,12 @@
       <c r="Q7" s="9" t="n"/>
       <c r="R7" s="9" t="n"/>
       <c r="S7" s="9" t="n"/>
-      <c r="T7" s="22" t="n"/>
+      <c r="T7" s="9" t="n"/>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="9" t="n"/>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1870,7 +2078,12 @@
       <c r="Q8" s="13" t="n"/>
       <c r="R8" s="13" t="n"/>
       <c r="S8" s="13" t="n"/>
-      <c r="T8" s="24" t="n"/>
+      <c r="T8" s="13" t="n"/>
+      <c r="U8" s="13" t="n"/>
+      <c r="V8" s="13" t="n"/>
+      <c r="W8" s="13" t="n"/>
+      <c r="X8" s="13" t="n"/>
+      <c r="Y8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1930,7 +2143,12 @@
       <c r="Q9" s="9" t="n"/>
       <c r="R9" s="9" t="n"/>
       <c r="S9" s="9" t="n"/>
-      <c r="T9" s="22" t="n"/>
+      <c r="T9" s="9" t="n"/>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="9" t="n"/>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1990,7 +2208,12 @@
       <c r="Q10" s="13" t="n"/>
       <c r="R10" s="13" t="n"/>
       <c r="S10" s="13" t="n"/>
-      <c r="T10" s="24" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="13" t="n"/>
+      <c r="V10" s="13" t="n"/>
+      <c r="W10" s="13" t="n"/>
+      <c r="X10" s="13" t="n"/>
+      <c r="Y10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -2050,7 +2273,12 @@
       <c r="Q11" s="9" t="n"/>
       <c r="R11" s="9" t="n"/>
       <c r="S11" s="9" t="n"/>
-      <c r="T11" s="22" t="n"/>
+      <c r="T11" s="9" t="n"/>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="9" t="n"/>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -2110,7 +2338,12 @@
       <c r="Q12" s="13" t="n"/>
       <c r="R12" s="13" t="n"/>
       <c r="S12" s="13" t="n"/>
-      <c r="T12" s="24" t="n"/>
+      <c r="T12" s="13" t="n"/>
+      <c r="U12" s="13" t="n"/>
+      <c r="V12" s="13" t="n"/>
+      <c r="W12" s="13" t="n"/>
+      <c r="X12" s="13" t="n"/>
+      <c r="Y12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -2170,7 +2403,12 @@
       <c r="Q13" s="9" t="n"/>
       <c r="R13" s="9" t="n"/>
       <c r="S13" s="9" t="n"/>
-      <c r="T13" s="22" t="n"/>
+      <c r="T13" s="9" t="n"/>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="9" t="n"/>
+      <c r="W13" s="9" t="n"/>
+      <c r="X13" s="9" t="n"/>
+      <c r="Y13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -2230,7 +2468,12 @@
       <c r="Q14" s="13" t="n"/>
       <c r="R14" s="13" t="n"/>
       <c r="S14" s="13" t="n"/>
-      <c r="T14" s="24" t="n"/>
+      <c r="T14" s="13" t="n"/>
+      <c r="U14" s="13" t="n"/>
+      <c r="V14" s="13" t="n"/>
+      <c r="W14" s="13" t="n"/>
+      <c r="X14" s="13" t="n"/>
+      <c r="Y14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -2290,7 +2533,12 @@
       <c r="Q15" s="9" t="n"/>
       <c r="R15" s="9" t="n"/>
       <c r="S15" s="9" t="n"/>
-      <c r="T15" s="22" t="n"/>
+      <c r="T15" s="9" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="9" t="n"/>
+      <c r="X15" s="9" t="n"/>
+      <c r="Y15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -2350,7 +2598,12 @@
       <c r="Q16" s="13" t="n"/>
       <c r="R16" s="13" t="n"/>
       <c r="S16" s="13" t="n"/>
-      <c r="T16" s="24" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="13" t="n"/>
+      <c r="V16" s="13" t="n"/>
+      <c r="W16" s="13" t="n"/>
+      <c r="X16" s="13" t="n"/>
+      <c r="Y16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -2410,7 +2663,12 @@
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
       <c r="S17" s="9" t="n"/>
-      <c r="T17" s="22" t="n"/>
+      <c r="T17" s="9" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="9" t="n"/>
+      <c r="W17" s="9" t="n"/>
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -2470,7 +2728,12 @@
       <c r="Q18" s="13" t="n"/>
       <c r="R18" s="13" t="n"/>
       <c r="S18" s="13" t="n"/>
-      <c r="T18" s="24" t="n"/>
+      <c r="T18" s="13" t="n"/>
+      <c r="U18" s="13" t="n"/>
+      <c r="V18" s="13" t="n"/>
+      <c r="W18" s="13" t="n"/>
+      <c r="X18" s="13" t="n"/>
+      <c r="Y18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2530,7 +2793,12 @@
       <c r="Q19" s="9" t="n"/>
       <c r="R19" s="9" t="n"/>
       <c r="S19" s="9" t="n"/>
-      <c r="T19" s="22" t="n"/>
+      <c r="T19" s="9" t="n"/>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="9" t="n"/>
+      <c r="W19" s="9" t="n"/>
+      <c r="X19" s="9" t="n"/>
+      <c r="Y19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2590,7 +2858,12 @@
       <c r="Q20" s="13" t="n"/>
       <c r="R20" s="13" t="n"/>
       <c r="S20" s="13" t="n"/>
-      <c r="T20" s="24" t="n"/>
+      <c r="T20" s="13" t="n"/>
+      <c r="U20" s="13" t="n"/>
+      <c r="V20" s="13" t="n"/>
+      <c r="W20" s="13" t="n"/>
+      <c r="X20" s="13" t="n"/>
+      <c r="Y20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2650,7 +2923,12 @@
       <c r="Q21" s="9" t="n"/>
       <c r="R21" s="9" t="n"/>
       <c r="S21" s="9" t="n"/>
-      <c r="T21" s="22" t="n"/>
+      <c r="T21" s="9" t="n"/>
+      <c r="U21" s="9" t="n"/>
+      <c r="V21" s="9" t="n"/>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="9" t="n"/>
+      <c r="Y21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2710,7 +2988,12 @@
       <c r="Q22" s="13" t="n"/>
       <c r="R22" s="13" t="n"/>
       <c r="S22" s="13" t="n"/>
-      <c r="T22" s="24" t="n"/>
+      <c r="T22" s="13" t="n"/>
+      <c r="U22" s="13" t="n"/>
+      <c r="V22" s="13" t="n"/>
+      <c r="W22" s="13" t="n"/>
+      <c r="X22" s="13" t="n"/>
+      <c r="Y22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2770,7 +3053,12 @@
       <c r="Q23" s="9" t="n"/>
       <c r="R23" s="9" t="n"/>
       <c r="S23" s="9" t="n"/>
-      <c r="T23" s="22" t="n"/>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="9" t="n"/>
+      <c r="V23" s="9" t="n"/>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="9" t="n"/>
+      <c r="Y23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2830,7 +3118,12 @@
       <c r="Q24" s="13" t="n"/>
       <c r="R24" s="13" t="n"/>
       <c r="S24" s="13" t="n"/>
-      <c r="T24" s="24" t="n"/>
+      <c r="T24" s="13" t="n"/>
+      <c r="U24" s="13" t="n"/>
+      <c r="V24" s="13" t="n"/>
+      <c r="W24" s="13" t="n"/>
+      <c r="X24" s="13" t="n"/>
+      <c r="Y24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2890,7 +3183,12 @@
       <c r="Q25" s="9" t="n"/>
       <c r="R25" s="9" t="n"/>
       <c r="S25" s="9" t="n"/>
-      <c r="T25" s="22" t="n"/>
+      <c r="T25" s="9" t="n"/>
+      <c r="U25" s="9" t="n"/>
+      <c r="V25" s="9" t="n"/>
+      <c r="W25" s="9" t="n"/>
+      <c r="X25" s="9" t="n"/>
+      <c r="Y25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2950,7 +3248,12 @@
       <c r="Q26" s="13" t="n"/>
       <c r="R26" s="13" t="n"/>
       <c r="S26" s="13" t="n"/>
-      <c r="T26" s="24" t="n"/>
+      <c r="T26" s="13" t="n"/>
+      <c r="U26" s="13" t="n"/>
+      <c r="V26" s="13" t="n"/>
+      <c r="W26" s="13" t="n"/>
+      <c r="X26" s="13" t="n"/>
+      <c r="Y26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -3010,7 +3313,12 @@
       <c r="Q27" s="9" t="n"/>
       <c r="R27" s="9" t="n"/>
       <c r="S27" s="9" t="n"/>
-      <c r="T27" s="22" t="n"/>
+      <c r="T27" s="9" t="n"/>
+      <c r="U27" s="9" t="n"/>
+      <c r="V27" s="9" t="n"/>
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="9" t="n"/>
+      <c r="Y27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n"/>
@@ -3032,7 +3340,12 @@
       <c r="Q28" s="13" t="n"/>
       <c r="R28" s="13" t="n"/>
       <c r="S28" s="13" t="n"/>
-      <c r="T28" s="24" t="n"/>
+      <c r="T28" s="13" t="n"/>
+      <c r="U28" s="13" t="n"/>
+      <c r="V28" s="13" t="n"/>
+      <c r="W28" s="13" t="n"/>
+      <c r="X28" s="13" t="n"/>
+      <c r="Y28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n"/>
@@ -3054,7 +3367,12 @@
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
       <c r="S29" s="9" t="n"/>
-      <c r="T29" s="22" t="n"/>
+      <c r="T29" s="9" t="n"/>
+      <c r="U29" s="9" t="n"/>
+      <c r="V29" s="9" t="n"/>
+      <c r="W29" s="9" t="n"/>
+      <c r="X29" s="9" t="n"/>
+      <c r="Y29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n"/>
@@ -3076,7 +3394,12 @@
       <c r="Q30" s="13" t="n"/>
       <c r="R30" s="13" t="n"/>
       <c r="S30" s="13" t="n"/>
-      <c r="T30" s="24" t="n"/>
+      <c r="T30" s="13" t="n"/>
+      <c r="U30" s="13" t="n"/>
+      <c r="V30" s="13" t="n"/>
+      <c r="W30" s="13" t="n"/>
+      <c r="X30" s="13" t="n"/>
+      <c r="Y30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n"/>
@@ -3098,7 +3421,12 @@
       <c r="Q31" s="9" t="n"/>
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="9" t="n"/>
-      <c r="T31" s="22" t="n"/>
+      <c r="T31" s="9" t="n"/>
+      <c r="U31" s="9" t="n"/>
+      <c r="V31" s="9" t="n"/>
+      <c r="W31" s="9" t="n"/>
+      <c r="X31" s="9" t="n"/>
+      <c r="Y31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n"/>
@@ -3120,7 +3448,12 @@
       <c r="Q32" s="13" t="n"/>
       <c r="R32" s="13" t="n"/>
       <c r="S32" s="13" t="n"/>
-      <c r="T32" s="24" t="n"/>
+      <c r="T32" s="13" t="n"/>
+      <c r="U32" s="13" t="n"/>
+      <c r="V32" s="13" t="n"/>
+      <c r="W32" s="13" t="n"/>
+      <c r="X32" s="13" t="n"/>
+      <c r="Y32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n"/>
@@ -3142,7 +3475,12 @@
       <c r="Q33" s="9" t="n"/>
       <c r="R33" s="9" t="n"/>
       <c r="S33" s="9" t="n"/>
-      <c r="T33" s="22" t="n"/>
+      <c r="T33" s="9" t="n"/>
+      <c r="U33" s="9" t="n"/>
+      <c r="V33" s="9" t="n"/>
+      <c r="W33" s="9" t="n"/>
+      <c r="X33" s="9" t="n"/>
+      <c r="Y33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n"/>
@@ -3164,7 +3502,12 @@
       <c r="Q34" s="13" t="n"/>
       <c r="R34" s="13" t="n"/>
       <c r="S34" s="13" t="n"/>
-      <c r="T34" s="24" t="n"/>
+      <c r="T34" s="13" t="n"/>
+      <c r="U34" s="13" t="n"/>
+      <c r="V34" s="13" t="n"/>
+      <c r="W34" s="13" t="n"/>
+      <c r="X34" s="13" t="n"/>
+      <c r="Y34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n"/>
@@ -3186,7 +3529,12 @@
       <c r="Q35" s="9" t="n"/>
       <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n"/>
-      <c r="T35" s="22" t="n"/>
+      <c r="T35" s="9" t="n"/>
+      <c r="U35" s="9" t="n"/>
+      <c r="V35" s="9" t="n"/>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="9" t="n"/>
+      <c r="Y35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n"/>
@@ -3208,7 +3556,12 @@
       <c r="Q36" s="13" t="n"/>
       <c r="R36" s="13" t="n"/>
       <c r="S36" s="13" t="n"/>
-      <c r="T36" s="24" t="n"/>
+      <c r="T36" s="13" t="n"/>
+      <c r="U36" s="13" t="n"/>
+      <c r="V36" s="13" t="n"/>
+      <c r="W36" s="13" t="n"/>
+      <c r="X36" s="13" t="n"/>
+      <c r="Y36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n"/>
@@ -3230,7 +3583,12 @@
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="9" t="n"/>
-      <c r="T37" s="22" t="n"/>
+      <c r="T37" s="9" t="n"/>
+      <c r="U37" s="9" t="n"/>
+      <c r="V37" s="9" t="n"/>
+      <c r="W37" s="9" t="n"/>
+      <c r="X37" s="9" t="n"/>
+      <c r="Y37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n"/>
@@ -3252,7 +3610,12 @@
       <c r="Q38" s="13" t="n"/>
       <c r="R38" s="13" t="n"/>
       <c r="S38" s="13" t="n"/>
-      <c r="T38" s="24" t="n"/>
+      <c r="T38" s="13" t="n"/>
+      <c r="U38" s="13" t="n"/>
+      <c r="V38" s="13" t="n"/>
+      <c r="W38" s="13" t="n"/>
+      <c r="X38" s="13" t="n"/>
+      <c r="Y38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n"/>
@@ -3274,7 +3637,12 @@
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="9" t="n"/>
-      <c r="T39" s="22" t="n"/>
+      <c r="T39" s="9" t="n"/>
+      <c r="U39" s="9" t="n"/>
+      <c r="V39" s="9" t="n"/>
+      <c r="W39" s="9" t="n"/>
+      <c r="X39" s="9" t="n"/>
+      <c r="Y39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n"/>
@@ -3296,7 +3664,12 @@
       <c r="Q40" s="13" t="n"/>
       <c r="R40" s="13" t="n"/>
       <c r="S40" s="13" t="n"/>
-      <c r="T40" s="24" t="n"/>
+      <c r="T40" s="13" t="n"/>
+      <c r="U40" s="13" t="n"/>
+      <c r="V40" s="13" t="n"/>
+      <c r="W40" s="13" t="n"/>
+      <c r="X40" s="13" t="n"/>
+      <c r="Y40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n"/>
@@ -3318,7 +3691,12 @@
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="9" t="n"/>
-      <c r="T41" s="22" t="n"/>
+      <c r="T41" s="9" t="n"/>
+      <c r="U41" s="9" t="n"/>
+      <c r="V41" s="9" t="n"/>
+      <c r="W41" s="9" t="n"/>
+      <c r="X41" s="9" t="n"/>
+      <c r="Y41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n"/>
@@ -3340,7 +3718,12 @@
       <c r="Q42" s="13" t="n"/>
       <c r="R42" s="13" t="n"/>
       <c r="S42" s="13" t="n"/>
-      <c r="T42" s="24" t="n"/>
+      <c r="T42" s="13" t="n"/>
+      <c r="U42" s="13" t="n"/>
+      <c r="V42" s="13" t="n"/>
+      <c r="W42" s="13" t="n"/>
+      <c r="X42" s="13" t="n"/>
+      <c r="Y42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n"/>
@@ -3362,7 +3745,12 @@
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
       <c r="S43" s="9" t="n"/>
-      <c r="T43" s="22" t="n"/>
+      <c r="T43" s="9" t="n"/>
+      <c r="U43" s="9" t="n"/>
+      <c r="V43" s="9" t="n"/>
+      <c r="W43" s="9" t="n"/>
+      <c r="X43" s="9" t="n"/>
+      <c r="Y43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n"/>
@@ -3384,7 +3772,12 @@
       <c r="Q44" s="13" t="n"/>
       <c r="R44" s="13" t="n"/>
       <c r="S44" s="13" t="n"/>
-      <c r="T44" s="24" t="n"/>
+      <c r="T44" s="13" t="n"/>
+      <c r="U44" s="13" t="n"/>
+      <c r="V44" s="13" t="n"/>
+      <c r="W44" s="13" t="n"/>
+      <c r="X44" s="13" t="n"/>
+      <c r="Y44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n"/>
@@ -3406,7 +3799,12 @@
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
       <c r="S45" s="9" t="n"/>
-      <c r="T45" s="22" t="n"/>
+      <c r="T45" s="9" t="n"/>
+      <c r="U45" s="9" t="n"/>
+      <c r="V45" s="9" t="n"/>
+      <c r="W45" s="9" t="n"/>
+      <c r="X45" s="9" t="n"/>
+      <c r="Y45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n"/>
@@ -3428,7 +3826,12 @@
       <c r="Q46" s="13" t="n"/>
       <c r="R46" s="13" t="n"/>
       <c r="S46" s="13" t="n"/>
-      <c r="T46" s="24" t="n"/>
+      <c r="T46" s="13" t="n"/>
+      <c r="U46" s="13" t="n"/>
+      <c r="V46" s="13" t="n"/>
+      <c r="W46" s="13" t="n"/>
+      <c r="X46" s="13" t="n"/>
+      <c r="Y46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n"/>
@@ -3450,7 +3853,12 @@
       <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
       <c r="S47" s="9" t="n"/>
-      <c r="T47" s="22" t="n"/>
+      <c r="T47" s="9" t="n"/>
+      <c r="U47" s="9" t="n"/>
+      <c r="V47" s="9" t="n"/>
+      <c r="W47" s="9" t="n"/>
+      <c r="X47" s="9" t="n"/>
+      <c r="Y47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n"/>
@@ -3472,7 +3880,12 @@
       <c r="Q48" s="13" t="n"/>
       <c r="R48" s="13" t="n"/>
       <c r="S48" s="13" t="n"/>
-      <c r="T48" s="24" t="n"/>
+      <c r="T48" s="13" t="n"/>
+      <c r="U48" s="13" t="n"/>
+      <c r="V48" s="13" t="n"/>
+      <c r="W48" s="13" t="n"/>
+      <c r="X48" s="13" t="n"/>
+      <c r="Y48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n"/>
@@ -3494,7 +3907,12 @@
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="9" t="n"/>
-      <c r="T49" s="22" t="n"/>
+      <c r="T49" s="9" t="n"/>
+      <c r="U49" s="9" t="n"/>
+      <c r="V49" s="9" t="n"/>
+      <c r="W49" s="9" t="n"/>
+      <c r="X49" s="9" t="n"/>
+      <c r="Y49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n"/>
@@ -3516,7 +3934,12 @@
       <c r="Q50" s="13" t="n"/>
       <c r="R50" s="13" t="n"/>
       <c r="S50" s="13" t="n"/>
-      <c r="T50" s="24" t="n"/>
+      <c r="T50" s="13" t="n"/>
+      <c r="U50" s="13" t="n"/>
+      <c r="V50" s="13" t="n"/>
+      <c r="W50" s="13" t="n"/>
+      <c r="X50" s="13" t="n"/>
+      <c r="Y50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n"/>
@@ -3538,7 +3961,12 @@
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n"/>
-      <c r="T51" s="22" t="n"/>
+      <c r="T51" s="9" t="n"/>
+      <c r="U51" s="9" t="n"/>
+      <c r="V51" s="9" t="n"/>
+      <c r="W51" s="9" t="n"/>
+      <c r="X51" s="9" t="n"/>
+      <c r="Y51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n"/>
@@ -3560,7 +3988,12 @@
       <c r="Q52" s="13" t="n"/>
       <c r="R52" s="13" t="n"/>
       <c r="S52" s="13" t="n"/>
-      <c r="T52" s="24" t="n"/>
+      <c r="T52" s="13" t="n"/>
+      <c r="U52" s="13" t="n"/>
+      <c r="V52" s="13" t="n"/>
+      <c r="W52" s="13" t="n"/>
+      <c r="X52" s="13" t="n"/>
+      <c r="Y52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n"/>
@@ -3582,7 +4015,12 @@
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
       <c r="S53" s="9" t="n"/>
-      <c r="T53" s="22" t="n"/>
+      <c r="T53" s="9" t="n"/>
+      <c r="U53" s="9" t="n"/>
+      <c r="V53" s="9" t="n"/>
+      <c r="W53" s="9" t="n"/>
+      <c r="X53" s="9" t="n"/>
+      <c r="Y53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n"/>
@@ -3604,7 +4042,12 @@
       <c r="Q54" s="13" t="n"/>
       <c r="R54" s="13" t="n"/>
       <c r="S54" s="13" t="n"/>
-      <c r="T54" s="24" t="n"/>
+      <c r="T54" s="13" t="n"/>
+      <c r="U54" s="13" t="n"/>
+      <c r="V54" s="13" t="n"/>
+      <c r="W54" s="13" t="n"/>
+      <c r="X54" s="13" t="n"/>
+      <c r="Y54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n"/>
@@ -3626,7 +4069,12 @@
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
       <c r="S55" s="9" t="n"/>
-      <c r="T55" s="22" t="n"/>
+      <c r="T55" s="9" t="n"/>
+      <c r="U55" s="9" t="n"/>
+      <c r="V55" s="9" t="n"/>
+      <c r="W55" s="9" t="n"/>
+      <c r="X55" s="9" t="n"/>
+      <c r="Y55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n"/>
@@ -3648,7 +4096,12 @@
       <c r="Q56" s="13" t="n"/>
       <c r="R56" s="13" t="n"/>
       <c r="S56" s="13" t="n"/>
-      <c r="T56" s="24" t="n"/>
+      <c r="T56" s="13" t="n"/>
+      <c r="U56" s="13" t="n"/>
+      <c r="V56" s="13" t="n"/>
+      <c r="W56" s="13" t="n"/>
+      <c r="X56" s="13" t="n"/>
+      <c r="Y56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n"/>
@@ -3670,14 +4123,19 @@
       <c r="Q57" s="9" t="n"/>
       <c r="R57" s="9" t="n"/>
       <c r="S57" s="9" t="n"/>
-      <c r="T57" s="22" t="n"/>
+      <c r="T57" s="9" t="n"/>
+      <c r="U57" s="9" t="n"/>
+      <c r="V57" s="9" t="n"/>
+      <c r="W57" s="9" t="n"/>
+      <c r="X57" s="9" t="n"/>
+      <c r="Y57" s="22" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="W2:Y2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="Q5:Q28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/02_자동화_완제품/KNK_자동화_완제품_구매팀_입력_2026.xlsx
@@ -66,7 +66,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +121,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000277BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF6C00"/>
       </patternFill>
     </fill>
   </fills>
@@ -237,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -569,6 +579,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1500,7 +1525,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="109" t="inlineStr">
+      <c r="A1" s="112" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 자동화_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1531,7 +1556,7 @@
       <c r="Y1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="110" t="inlineStr">
+      <c r="A2" s="113" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  자동화 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1557,9 +1582,9 @@
       <c r="T2" s="16" t="n"/>
       <c r="U2" s="16" t="n"/>
       <c r="V2" s="17" t="n"/>
-      <c r="W2" s="111" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 14:35</t>
+      <c r="W2" s="114" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 15:15</t>
         </is>
       </c>
       <c r="X2" s="16" t="n"/>
@@ -1748,56 +1773,56 @@
           <t>부서진척률(%)</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="115" t="inlineStr">
         <is>
           <t>BOM
 작성</t>
         </is>
       </c>
-      <c r="M4" s="70" t="inlineStr">
+      <c r="M4" s="115" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="116" t="inlineStr">
         <is>
           <t>구매
 검토</t>
         </is>
       </c>
-      <c r="O4" s="70" t="inlineStr">
+      <c r="O4" s="116" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="P4" s="115" t="inlineStr">
         <is>
           <t>구매품
 발주</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="inlineStr">
+      <c r="Q4" s="115" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="R4" s="116" t="inlineStr">
         <is>
           <t>가공품
 발주</t>
         </is>
       </c>
-      <c r="S4" s="70" t="inlineStr">
+      <c r="S4" s="116" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
       </c>
-      <c r="T4" s="7" t="inlineStr">
+      <c r="T4" s="115" t="inlineStr">
         <is>
           <t>입고</t>
         </is>
       </c>
-      <c r="U4" s="70" t="inlineStr">
+      <c r="U4" s="115" t="inlineStr">
         <is>
           <t>예정일</t>
         </is>
